--- a/tools/fixtures/면접관명단_sample.xlsx
+++ b/tools/fixtures/면접관명단_sample.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,20 +429,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>직급</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>소속팀</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>이메일</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>일일최대</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
@@ -461,18 +466,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>수석</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>AI솔루션팀</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>iv101@example.com</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>4</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -489,18 +499,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>책임</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>AI솔루션팀</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>iv102@example.com</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>6</v>
-      </c>
       <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -517,18 +532,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>선임</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>AI솔루션팀</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>iv103@example.com</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>6</v>
-      </c>
       <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -545,18 +565,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>선임</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>AI솔루션팀</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>iv104@example.com</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>6</v>
-      </c>
       <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -573,18 +598,23 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>수석</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>로봇응용기술팀</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>iv201@example.com</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -601,18 +631,23 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>책임</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>로봇응용기술팀</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>iv202@example.com</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>6</v>
-      </c>
       <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -629,18 +664,23 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>선임</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>로봇응용기술팀</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>iv203@example.com</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
       <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -657,18 +697,23 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>선임</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>로봇응용기술팀</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>iv204@example.com</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>6</v>
-      </c>
       <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="n">
         <v>2</v>
       </c>
     </row>
@@ -685,18 +730,23 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>수석</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>미래혁신팀</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>iv301@example.com</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>4</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -713,18 +763,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>책임</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>미래혁신팀</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>iv302@example.com</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>6</v>
-      </c>
       <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="n">
         <v>2</v>
       </c>
     </row>
@@ -741,18 +796,23 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>선임</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>미래혁신팀</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>iv303@example.com</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>6</v>
-      </c>
       <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="n">
         <v>2</v>
       </c>
     </row>
@@ -769,18 +829,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>선임</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>미래혁신팀</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>iv304@example.com</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>6</v>
-      </c>
       <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
         <v>2</v>
       </c>
     </row>
@@ -797,18 +862,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>수석</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>배터리기술팀</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>iv401@example.com</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>4</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -825,18 +895,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>책임</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>배터리기술팀</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>iv402@example.com</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>6</v>
-      </c>
       <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="n">
         <v>2</v>
       </c>
     </row>
@@ -853,18 +928,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>선임</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>배터리기술팀</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>iv403@example.com</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>6</v>
-      </c>
       <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -881,18 +961,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>선임</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>배터리기술팀</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>iv404@example.com</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>6</v>
-      </c>
       <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="n">
         <v>2</v>
       </c>
     </row>
@@ -909,18 +994,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>수석</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>전극기술팀</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>iv501@example.com</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>4</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -937,18 +1027,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>책임</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>전극기술팀</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>iv502@example.com</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>6</v>
-      </c>
       <c r="F19" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" t="n">
         <v>2</v>
       </c>
     </row>
@@ -965,18 +1060,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>선임</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>전극기술팀</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>iv503@example.com</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>6</v>
-      </c>
       <c r="F20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" t="n">
         <v>2</v>
       </c>
     </row>
@@ -993,18 +1093,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>선임</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>전극기술팀</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>iv504@example.com</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>6</v>
-      </c>
       <c r="F21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" t="n">
         <v>2</v>
       </c>
     </row>
